--- a/reports/Debug-purgatory-20260106/Week Total (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260106/Week Total (Prior Year)_Revenue.xlsx
@@ -106,16 +106,16 @@
     <t>account</t>
   </si>
   <si>
+    <t>T110</t>
+  </si>
+  <si>
+    <t>T105</t>
+  </si>
+  <si>
     <t>T100</t>
   </si>
   <si>
     <t>T101</t>
-  </si>
-  <si>
-    <t>T110</t>
-  </si>
-  <si>
-    <t>T105</t>
   </si>
   <si>
     <t>department</t>
@@ -602,7 +602,7 @@
         <v>35</v>
       </c>
       <c r="D2" s="2">
-        <v>325949.10</v>
+        <v>510.00</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -616,7 +616,7 @@
         <v>35</v>
       </c>
       <c r="D3" s="2">
-        <v>4224.30</v>
+        <v>348.00</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -630,7 +630,7 @@
         <v>35</v>
       </c>
       <c r="D4" s="2">
-        <v>510.00</v>
+        <v>325949.10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -644,7 +644,7 @@
         <v>35</v>
       </c>
       <c r="D5" s="2">
-        <v>348.00</v>
+        <v>4224.30</v>
       </c>
     </row>
     <row r="6" spans="1:4">
